--- a/annotators/team/tg/in-progress/an-online.de.224441.xlsx
+++ b/annotators/team/tg/in-progress/an-online.de.224441.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\preanno_parcor_coref\de\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\in-progress\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A8288D-6AB5-4083-AF06-9A3B43B42677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACC353A-8B92-4919-A8D3-6672C94572C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sentence-level annotation" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="498">
   <si>
     <t>ID</t>
   </si>
@@ -1304,9 +1304,6 @@
     <t>GEN</t>
   </si>
   <si>
-    <t>CHECK ob ID</t>
-  </si>
-  <si>
     <t>suedafrika</t>
   </si>
   <si>
@@ -1433,9 +1430,6 @@
     <t>preise&gt;bvk,slb,ctp</t>
   </si>
   <si>
-    <t>alternativ auch CAT denkbar</t>
-  </si>
-  <si>
     <t>samstag</t>
   </si>
   <si>
@@ -1445,9 +1439,6 @@
     <t>preisgeld</t>
   </si>
   <si>
-    <t>!!!</t>
-  </si>
-  <si>
     <t>hall_of_fame</t>
   </si>
   <si>
@@ -1458,6 +1449,72 @@
   </si>
   <si>
     <t>nicht syntaktischer Kopf</t>
+  </si>
+  <si>
+    <t>ID, weil später referenziert</t>
+  </si>
+  <si>
+    <t>ende_turnier</t>
+  </si>
+  <si>
+    <t>konkreter Zeitpunkt</t>
+  </si>
+  <si>
+    <t>auch GEN denkbar</t>
+  </si>
+  <si>
+    <t>ausritt</t>
+  </si>
+  <si>
+    <t>Antezedens für 51: es</t>
+  </si>
+  <si>
+    <t>futtertroege</t>
+  </si>
+  <si>
+    <t>galopp</t>
+  </si>
+  <si>
+    <t>ID, weil Antezedens für "dieses Tempo" in 98</t>
+  </si>
+  <si>
+    <t>parser error: nicht syntaktischer Kopf</t>
+  </si>
+  <si>
+    <t>reitkarriere</t>
+  </si>
+  <si>
+    <t>anlage_alrv</t>
+  </si>
+  <si>
+    <t>alrv</t>
+  </si>
+  <si>
+    <t>CHECK: unclear</t>
+  </si>
+  <si>
+    <t>IDIOM</t>
+  </si>
+  <si>
+    <t>alternativ auch CAT oder GEN denkbar</t>
+  </si>
+  <si>
+    <t>wrong sentence break</t>
+  </si>
+  <si>
+    <t>kein auto ref; CHECK ob CAT oder GROUP</t>
+  </si>
+  <si>
+    <t>ausgezeichnete</t>
+  </si>
+  <si>
+    <t>Untermenge der Ausgezeichneten</t>
+  </si>
+  <si>
+    <t>viele_sportler</t>
+  </si>
+  <si>
+    <t>off_teil</t>
   </si>
 </sst>
 </file>
@@ -2895,7 +2952,7 @@
         <v/>
       </c>
       <c r="L3" s="26" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -3013,7 +3070,7 @@
         <v>131</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F7" s="22" t="str">
         <f>IF(OR(E7="",E7="!!!"),"",IF(NOT(ISNA(VLOOKUP(E7,E$1:E6,1,FALSE()))),"OLD",IF(AND(E7&lt;&gt;"",E7&lt;&gt;"!!!"),"NEW","")))</f>
@@ -3092,7 +3149,7 @@
         <v>141</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F11" s="22" t="str">
         <f>IF(OR(E11="",E11="!!!"),"",IF(NOT(ISNA(VLOOKUP(E11,E$1:E10,1,FALSE()))),"OLD",IF(AND(E11&lt;&gt;"",E11&lt;&gt;"!!!"),"NEW","")))</f>
@@ -3125,7 +3182,7 @@
         <v>142</v>
       </c>
       <c r="E12" s="21" t="str">
-        <f t="shared" ref="E10:E17" si="1">IF(D12="?OLD","!!!","")</f>
+        <f t="shared" ref="E12:E17" si="1">IF(D12="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F12" s="22" t="str">
@@ -3202,7 +3259,7 @@
         <v>131</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F14" s="22" t="s">
         <v>426</v>
@@ -3228,7 +3285,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="L14" s="26" t="s">
-        <v>427</v>
+        <v>476</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
@@ -3419,35 +3476,35 @@
       <c r="D22" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E22" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>!!!</v>
-      </c>
-      <c r="F22" s="22" t="str">
-        <f>IF(OR(E22="",E22="!!!"),"",IF(NOT(ISNA(VLOOKUP(E22,E$1:E21,1,FALSE()))),"OLD",IF(AND(E22&lt;&gt;"",E22&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
-      </c>
-      <c r="G22" s="23" t="str">
-        <f>IF(OR(E22="",E22="!!!"),"",IF(OR(J22=0,AND(J22=1,K22=1),AND(J22=1,I22="SBJ"),AND(J22=1,I22=0)),"?IN_FOCUS",IF(J22&lt;=2,"?ACTIVATED",IF(J22&lt;&gt;"","?FAMILIAR",IF(F22="NEW",IF(ISNA(VLOOKUP(E22,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v/>
+      <c r="E22" s="21" t="s">
+        <v>477</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="G22" s="23" t="e">
+        <f ca="1">IF(OR(E22="",E22="!!!"),"",IF(OR(J22=0,AND(J22=1,K22=1),AND(J22=1,I22="SBJ"),AND(J22=1,I22=0)),"?IN_FOCUS",IF(J22&lt;=2,"?ACTIVATED",IF(J22&lt;&gt;"","?FAMILIAR",IF(F22="NEW",IF(ISNA(VLOOKUP(E22,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v>#VALUE!</v>
       </c>
       <c r="H22" s="24" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="I22" s="25" t="str">
+      <c r="I22" s="25" t="e">
         <f>IF(OR(E22="",E22="!!!",F22="NEW"),"",INDEX(B$2:B21,-1+SUMPRODUCT(MAX(ROW(E$2:E21)*(E22=E$2:E21)))))</f>
-        <v/>
-      </c>
-      <c r="J22" s="25" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J22" s="25">
         <f ca="1">IF(OR(E22="",E22="!!!",F22="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E22)*(E22=E$2:E22)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E21)*(E2=E$1:E21))))))</f>
-        <v/>
-      </c>
-      <c r="K22" s="25" t="str">
+        <v>0</v>
+      </c>
+      <c r="K22" s="25" t="e">
         <f>IF(OR(E22="",E22="!!!",F22="NEW"),"",INDEX(J$1:J21,SUMPRODUCT(MAX(ROW(E$1:E21)*(E22=E$1:E21)))))</f>
-        <v/>
-      </c>
-      <c r="L22" s="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L22" s="26" t="s">
+        <v>478</v>
+      </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
@@ -3571,7 +3628,7 @@
         <v>131</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F26" s="22" t="str">
         <f>IF(OR(E26="",E26="!!!"),"",IF(NOT(ISNA(VLOOKUP(E26,E$1:E25,1,FALSE()))),"OLD",IF(AND(E26&lt;&gt;"",E26&lt;&gt;"!!!"),"NEW","")))</f>
@@ -4009,17 +4066,16 @@
       <c r="C38" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="E38" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="E38" s="21" t="s">
+        <v>480</v>
       </c>
       <c r="F38" s="22" t="str">
         <f>IF(OR(E38="",E38="!!!"),"",IF(NOT(ISNA(VLOOKUP(E38,E$1:E37,1,FALSE()))),"OLD",IF(AND(E38&lt;&gt;"",E38&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
+        <v>NEW</v>
       </c>
       <c r="G38" s="23" t="str">
-        <f>IF(OR(E38="",E38="!!!"),"",IF(OR(J38=0,AND(J38=1,K38=1),AND(J38=1,I38="SBJ"),AND(J38=1,I38=0)),"?IN_FOCUS",IF(J38&lt;=2,"?ACTIVATED",IF(J38&lt;&gt;"","?FAMILIAR",IF(F38="NEW",IF(ISNA(VLOOKUP(E38,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v/>
+        <f ca="1">IF(OR(E38="",E38="!!!"),"",IF(OR(J38=0,AND(J38=1,K38=1),AND(J38=1,I38="SBJ"),AND(J38=1,I38=0)),"?IN_FOCUS",IF(J38&lt;=2,"?ACTIVATED",IF(J38&lt;&gt;"","?FAMILIAR",IF(F38="NEW",IF(ISNA(VLOOKUP(E38,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v>?REFERENTIAL</v>
       </c>
       <c r="H38" s="24" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -4037,7 +4093,9 @@
         <f>IF(OR(E38="",E38="!!!",F38="NEW"),"",INDEX(J$1:J37,SUMPRODUCT(MAX(ROW(E$1:E37)*(E38=E$1:E37)))))</f>
         <v/>
       </c>
-      <c r="L38" s="26"/>
+      <c r="L38" s="26" t="s">
+        <v>481</v>
+      </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
@@ -4121,7 +4179,7 @@
         <v>131</v>
       </c>
       <c r="E41" s="21" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F41" s="22" t="str">
         <f>IF(OR(E41="",E41="!!!"),"",IF(NOT(ISNA(VLOOKUP(E41,E$1:E40,1,FALSE()))),"OLD",IF(AND(E41&lt;&gt;"",E41&lt;&gt;"!!!"),"NEW","")))</f>
@@ -4147,7 +4205,9 @@
         <f>IF(OR(E41="",E41="!!!",F41="NEW"),"",INDEX(J$1:J40,SUMPRODUCT(MAX(ROW(E$1:E40)*(E41=E$1:E40)))))</f>
         <v/>
       </c>
-      <c r="L41" s="26"/>
+      <c r="L41" s="26" t="s">
+        <v>479</v>
+      </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
@@ -4413,17 +4473,16 @@
       <c r="D51" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E51" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v>!!!</v>
+      <c r="E51" s="21" t="s">
+        <v>480</v>
       </c>
       <c r="F51" s="22" t="str">
         <f>IF(OR(E51="",E51="!!!"),"",IF(NOT(ISNA(VLOOKUP(E51,E$1:E50,1,FALSE()))),"OLD",IF(AND(E51&lt;&gt;"",E51&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
+        <v>OLD</v>
       </c>
       <c r="G51" s="23" t="str">
-        <f>IF(OR(E51="",E51="!!!"),"",IF(OR(J51=0,AND(J51=1,K51=1),AND(J51=1,I51="SBJ"),AND(J51=1,I51=0)),"?IN_FOCUS",IF(J51&lt;=2,"?ACTIVATED",IF(J51&lt;&gt;"","?FAMILIAR",IF(F51="NEW",IF(ISNA(VLOOKUP(E51,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v/>
+        <f ca="1">IF(OR(E51="",E51="!!!"),"",IF(OR(J51=0,AND(J51=1,K51=1),AND(J51=1,I51="SBJ"),AND(J51=1,I51=0)),"?IN_FOCUS",IF(J51&lt;=2,"?ACTIVATED",IF(J51&lt;&gt;"","?FAMILIAR",IF(F51="NEW",IF(ISNA(VLOOKUP(E51,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v>?IN_FOCUS</v>
       </c>
       <c r="H51" s="24" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4431,14 +4490,14 @@
       </c>
       <c r="I51" s="25" t="str">
         <f>IF(OR(E51="",E51="!!!",F51="NEW"),"",INDEX(B$2:B50,-1+SUMPRODUCT(MAX(ROW(E$2:E50)*(E51=E$2:E50)))))</f>
-        <v/>
-      </c>
-      <c r="J51" s="25" t="str">
+        <v>other_2</v>
+      </c>
+      <c r="J51" s="25">
         <f ca="1">IF(OR(E51="",E51="!!!",F51="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E51)*(E51=E$2:E51)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E50)*(E2=E$1:E50))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K51" s="25" t="str">
-        <f>IF(OR(E51="",E51="!!!",F51="NEW"),"",INDEX(J$1:J50,SUMPRODUCT(MAX(ROW(E$1:E50)*(E51=E$1:E50)))))</f>
+        <f ca="1">IF(OR(E51="",E51="!!!",F51="NEW"),"",INDEX(J$1:J50,SUMPRODUCT(MAX(ROW(E$1:E50)*(E51=E$1:E50)))))</f>
         <v/>
       </c>
       <c r="L51" s="26"/>
@@ -4604,7 +4663,7 @@
         <v>131</v>
       </c>
       <c r="E58" s="21" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F58" s="22" t="str">
         <f>IF(OR(E58="",E58="!!!"),"",IF(NOT(ISNA(VLOOKUP(E58,E$1:E57,1,FALSE()))),"OLD",IF(AND(E58&lt;&gt;"",E58&lt;&gt;"!!!"),"NEW","")))</f>
@@ -4637,7 +4696,7 @@
         <v>186</v>
       </c>
       <c r="E59" s="21" t="str">
-        <f t="shared" ref="E58:E66" si="7">IF(D59="?OLD","!!!","")</f>
+        <f t="shared" ref="E59:E66" si="7">IF(D59="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F59" s="22" t="str">
@@ -4748,7 +4807,7 @@
         <v>131</v>
       </c>
       <c r="E62" s="21" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F62" s="22" t="str">
         <f>IF(OR(E62="",E62="!!!"),"",IF(NOT(ISNA(VLOOKUP(E62,E$1:E61,1,FALSE()))),"OLD",IF(AND(E62&lt;&gt;"",E62&lt;&gt;"!!!"),"NEW","")))</f>
@@ -5158,7 +5217,7 @@
         <v>131</v>
       </c>
       <c r="E75" s="21" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F75" s="22" t="str">
         <f>IF(OR(E75="",E75="!!!"),"",IF(NOT(ISNA(VLOOKUP(E75,E$1:E74,1,FALSE()))),"OLD",IF(AND(E75&lt;&gt;"",E75&lt;&gt;"!!!"),"NEW","")))</f>
@@ -5185,7 +5244,7 @@
         <v>0</v>
       </c>
       <c r="L75" s="26" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
@@ -5344,7 +5403,7 @@
         <v>131</v>
       </c>
       <c r="E80" s="21" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F80" s="22" t="str">
         <f>IF(OR(E80="",E80="!!!"),"",IF(NOT(ISNA(VLOOKUP(E80,E$1:E79,1,FALSE()))),"OLD",IF(AND(E80&lt;&gt;"",E80&lt;&gt;"!!!"),"NEW","")))</f>
@@ -5521,35 +5580,35 @@
       <c r="D85" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E85" s="21" t="str">
-        <f t="shared" si="8"/>
-        <v>!!!</v>
-      </c>
-      <c r="F85" s="22" t="str">
-        <f>IF(OR(E85="",E85="!!!"),"",IF(NOT(ISNA(VLOOKUP(E85,E$1:E84,1,FALSE()))),"OLD",IF(AND(E85&lt;&gt;"",E85&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
-      </c>
-      <c r="G85" s="23" t="str">
-        <f>IF(OR(E85="",E85="!!!"),"",IF(OR(J85=0,AND(J85=1,K85=1),AND(J85=1,I85="SBJ"),AND(J85=1,I85=0)),"?IN_FOCUS",IF(J85&lt;=2,"?ACTIVATED",IF(J85&lt;&gt;"","?FAMILIAR",IF(F85="NEW",IF(ISNA(VLOOKUP(E85,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v/>
+      <c r="E85" s="21" t="s">
+        <v>483</v>
+      </c>
+      <c r="F85" s="22" t="s">
+        <v>426</v>
+      </c>
+      <c r="G85" s="23" t="e">
+        <f ca="1">IF(OR(E85="",E85="!!!"),"",IF(OR(J85=0,AND(J85=1,K85=1),AND(J85=1,I85="SBJ"),AND(J85=1,I85=0)),"?IN_FOCUS",IF(J85&lt;=2,"?ACTIVATED",IF(J85&lt;&gt;"","?FAMILIAR",IF(F85="NEW",IF(ISNA(VLOOKUP(E85,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v>#VALUE!</v>
       </c>
       <c r="H85" s="24" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="I85" s="25" t="str">
+      <c r="I85" s="25" t="e">
         <f>IF(OR(E85="",E85="!!!",F85="NEW"),"",INDEX(B$2:B84,-1+SUMPRODUCT(MAX(ROW(E$2:E84)*(E85=E$2:E84)))))</f>
-        <v/>
-      </c>
-      <c r="J85" s="25" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J85" s="25">
         <f ca="1">IF(OR(E85="",E85="!!!",F85="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E85)*(E85=E$2:E85)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E84)*(E2=E$1:E84))))))</f>
-        <v/>
-      </c>
-      <c r="K85" s="25" t="str">
+        <v>0</v>
+      </c>
+      <c r="K85" s="25" t="e">
         <f>IF(OR(E85="",E85="!!!",F85="NEW"),"",INDEX(J$1:J84,SUMPRODUCT(MAX(ROW(E$1:E84)*(E85=E$1:E84)))))</f>
-        <v/>
-      </c>
-      <c r="L85" s="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L85" s="26" t="s">
+        <v>484</v>
+      </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
@@ -5712,17 +5771,16 @@
       <c r="D90" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E90" s="21" t="str">
-        <f t="shared" si="8"/>
-        <v>!!!</v>
+      <c r="E90" s="21" t="s">
+        <v>482</v>
       </c>
       <c r="F90" s="22" t="str">
         <f>IF(OR(E90="",E90="!!!"),"",IF(NOT(ISNA(VLOOKUP(E90,E$1:E89,1,FALSE()))),"OLD",IF(AND(E90&lt;&gt;"",E90&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
+        <v>NEW</v>
       </c>
       <c r="G90" s="23" t="str">
-        <f>IF(OR(E90="",E90="!!!"),"",IF(OR(J90=0,AND(J90=1,K90=1),AND(J90=1,I90="SBJ"),AND(J90=1,I90=0)),"?IN_FOCUS",IF(J90&lt;=2,"?ACTIVATED",IF(J90&lt;&gt;"","?FAMILIAR",IF(F90="NEW",IF(ISNA(VLOOKUP(E90,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v/>
+        <f ca="1">IF(OR(E90="",E90="!!!"),"",IF(OR(J90=0,AND(J90=1,K90=1),AND(J90=1,I90="SBJ"),AND(J90=1,I90=0)),"?IN_FOCUS",IF(J90&lt;=2,"?ACTIVATED",IF(J90&lt;&gt;"","?FAMILIAR",IF(F90="NEW",IF(ISNA(VLOOKUP(E90,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v>?REFERENTIAL</v>
       </c>
       <c r="H90" s="24" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -5928,7 +5986,7 @@
         <v/>
       </c>
       <c r="L97" s="26" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
@@ -5944,17 +6002,16 @@
       <c r="D98" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E98" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v>!!!</v>
+      <c r="E98" s="21" t="s">
+        <v>483</v>
       </c>
       <c r="F98" s="22" t="str">
         <f>IF(OR(E98="",E98="!!!"),"",IF(NOT(ISNA(VLOOKUP(E98,E$1:E97,1,FALSE()))),"OLD",IF(AND(E98&lt;&gt;"",E98&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
+        <v>OLD</v>
       </c>
       <c r="G98" s="23" t="str">
-        <f>IF(OR(E98="",E98="!!!"),"",IF(OR(J98=0,AND(J98=1,K98=1),AND(J98=1,I98="SBJ"),AND(J98=1,I98=0)),"?IN_FOCUS",IF(J98&lt;=2,"?ACTIVATED",IF(J98&lt;&gt;"","?FAMILIAR",IF(F98="NEW",IF(ISNA(VLOOKUP(E98,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v/>
+        <f ca="1">IF(OR(E98="",E98="!!!"),"",IF(OR(J98=0,AND(J98=1,K98=1),AND(J98=1,I98="SBJ"),AND(J98=1,I98=0)),"?IN_FOCUS",IF(J98&lt;=2,"?ACTIVATED",IF(J98&lt;&gt;"","?FAMILIAR",IF(F98="NEW",IF(ISNA(VLOOKUP(E98,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v>?IN_FOCUS</v>
       </c>
       <c r="H98" s="24" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -5962,15 +6019,15 @@
       </c>
       <c r="I98" s="25" t="str">
         <f>IF(OR(E98="",E98="!!!",F98="NEW"),"",INDEX(B$2:B97,-1+SUMPRODUCT(MAX(ROW(E$2:E97)*(E98=E$2:E97)))))</f>
-        <v/>
-      </c>
-      <c r="J98" s="25" t="str">
+        <v>other_2</v>
+      </c>
+      <c r="J98" s="25">
         <f ca="1">IF(OR(E98="",E98="!!!",F98="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E98)*(E98=E$2:E98)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E97)*(E2=E$1:E97))))))</f>
-        <v/>
-      </c>
-      <c r="K98" s="25" t="str">
-        <f>IF(OR(E98="",E98="!!!",F98="NEW"),"",INDEX(J$1:J97,SUMPRODUCT(MAX(ROW(E$1:E97)*(E98=E$1:E97)))))</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="K98" s="25">
+        <f ca="1">IF(OR(E98="",E98="!!!",F98="NEW"),"",INDEX(J$1:J97,SUMPRODUCT(MAX(ROW(E$1:E97)*(E98=E$1:E97)))))</f>
+        <v>0</v>
       </c>
       <c r="L98" s="26"/>
     </row>
@@ -6278,17 +6335,16 @@
       <c r="D109" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E109" s="21" t="str">
-        <f t="shared" si="12"/>
-        <v>!!!</v>
+      <c r="E109" s="21" t="s">
+        <v>480</v>
       </c>
       <c r="F109" s="22" t="str">
         <f>IF(OR(E109="",E109="!!!"),"",IF(NOT(ISNA(VLOOKUP(E109,E$1:E108,1,FALSE()))),"OLD",IF(AND(E109&lt;&gt;"",E109&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
+        <v>OLD</v>
       </c>
       <c r="G109" s="23" t="str">
-        <f>IF(OR(E109="",E109="!!!"),"",IF(OR(J109=0,AND(J109=1,K109=1),AND(J109=1,I109="SBJ"),AND(J109=1,I109=0)),"?IN_FOCUS",IF(J109&lt;=2,"?ACTIVATED",IF(J109&lt;&gt;"","?FAMILIAR",IF(F109="NEW",IF(ISNA(VLOOKUP(E109,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v/>
+        <f ca="1">IF(OR(E109="",E109="!!!"),"",IF(OR(J109=0,AND(J109=1,K109=1),AND(J109=1,I109="SBJ"),AND(J109=1,I109=0)),"?IN_FOCUS",IF(J109&lt;=2,"?ACTIVATED",IF(J109&lt;&gt;"","?FAMILIAR",IF(F109="NEW",IF(ISNA(VLOOKUP(E109,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v>?IN_FOCUS</v>
       </c>
       <c r="H109" s="24" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -6296,15 +6352,15 @@
       </c>
       <c r="I109" s="25" t="str">
         <f>IF(OR(E109="",E109="!!!",F109="NEW"),"",INDEX(B$2:B108,-1+SUMPRODUCT(MAX(ROW(E$2:E108)*(E109=E$2:E108)))))</f>
-        <v/>
-      </c>
-      <c r="J109" s="25" t="str">
+        <v>SBJ</v>
+      </c>
+      <c r="J109" s="25">
         <f ca="1">IF(OR(E109="",E109="!!!",F109="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E109)*(E109=E$2:E109)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E108)*(E2=E$1:E108))))))</f>
-        <v/>
-      </c>
-      <c r="K109" s="25" t="str">
-        <f>IF(OR(E109="",E109="!!!",F109="NEW"),"",INDEX(J$1:J108,SUMPRODUCT(MAX(ROW(E$1:E108)*(E109=E$1:E108)))))</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="K109" s="25">
+        <f ca="1">IF(OR(E109="",E109="!!!",F109="NEW"),"",INDEX(J$1:J108,SUMPRODUCT(MAX(ROW(E$1:E108)*(E109=E$1:E108)))))</f>
+        <v>0</v>
       </c>
       <c r="L109" s="26"/>
     </row>
@@ -6355,10 +6411,7 @@
       <c r="D111" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E111" s="21" t="str">
-        <f t="shared" si="12"/>
-        <v>!!!</v>
-      </c>
+      <c r="E111" s="21"/>
       <c r="F111" s="22" t="str">
         <f>IF(OR(E111="",E111="!!!"),"",IF(NOT(ISNA(VLOOKUP(E111,E$1:E110,1,FALSE()))),"OLD",IF(AND(E111&lt;&gt;"",E111&lt;&gt;"!!!"),"NEW","")))</f>
         <v/>
@@ -6383,7 +6436,9 @@
         <f>IF(OR(E111="",E111="!!!",F111="NEW"),"",INDEX(J$1:J110,SUMPRODUCT(MAX(ROW(E$1:E110)*(E111=E$1:E110)))))</f>
         <v/>
       </c>
-      <c r="L111" s="26"/>
+      <c r="L111" s="26" t="s">
+        <v>485</v>
+      </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
@@ -6433,9 +6488,8 @@
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="F113" s="22" t="str">
-        <f>IF(OR(E113="",E113="!!!"),"",IF(NOT(ISNA(VLOOKUP(E113,E$1:E112,1,FALSE()))),"OLD",IF(AND(E113&lt;&gt;"",E113&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
+      <c r="F113" s="22" t="s">
+        <v>436</v>
       </c>
       <c r="G113" s="23" t="str">
         <f>IF(OR(E113="",E113="!!!"),"",IF(OR(J113=0,AND(J113=1,K113=1),AND(J113=1,I113="SBJ"),AND(J113=1,I113=0)),"?IN_FOCUS",IF(J113&lt;=2,"?ACTIVATED",IF(J113&lt;&gt;"","?FAMILIAR",IF(F113="NEW",IF(ISNA(VLOOKUP(E113,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
@@ -6457,7 +6511,9 @@
         <f>IF(OR(E113="",E113="!!!",F113="NEW"),"",INDEX(J$1:J112,SUMPRODUCT(MAX(ROW(E$1:E112)*(E113=E$1:E112)))))</f>
         <v/>
       </c>
-      <c r="L113" s="26"/>
+      <c r="L113" s="26" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
@@ -6790,17 +6846,16 @@
       <c r="D125" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E125" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v>!!!</v>
+      <c r="E125" s="21" t="s">
+        <v>486</v>
       </c>
       <c r="F125" s="22" t="str">
         <f>IF(OR(E125="",E125="!!!"),"",IF(NOT(ISNA(VLOOKUP(E125,E$1:E124,1,FALSE()))),"OLD",IF(AND(E125&lt;&gt;"",E125&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
+        <v>NEW</v>
       </c>
       <c r="G125" s="23" t="str">
-        <f>IF(OR(E125="",E125="!!!"),"",IF(OR(J125=0,AND(J125=1,K125=1),AND(J125=1,I125="SBJ"),AND(J125=1,I125=0)),"?IN_FOCUS",IF(J125&lt;=2,"?ACTIVATED",IF(J125&lt;&gt;"","?FAMILIAR",IF(F125="NEW",IF(ISNA(VLOOKUP(E125,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v/>
+        <f ca="1">IF(OR(E125="",E125="!!!"),"",IF(OR(J125=0,AND(J125=1,K125=1),AND(J125=1,I125="SBJ"),AND(J125=1,I125=0)),"?IN_FOCUS",IF(J125&lt;=2,"?ACTIVATED",IF(J125&lt;&gt;"","?FAMILIAR",IF(F125="NEW",IF(ISNA(VLOOKUP(E125,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v>?REFERENTIAL</v>
       </c>
       <c r="H125" s="24" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -7077,10 +7132,10 @@
         <v>131</v>
       </c>
       <c r="E135" s="21" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F135" s="22" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G135" s="23" t="e">
         <f ca="1">IF(OR(E135="",E135="!!!"),"",IF(OR(J135=0,AND(J135=1,K135=1),AND(J135=1,I135="SBJ"),AND(J135=1,I135=0)),"?IN_FOCUS",IF(J135&lt;=2,"?ACTIVATED",IF(J135&lt;&gt;"","?FAMILIAR",IF(F135="NEW",IF(ISNA(VLOOKUP(E135,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
@@ -7152,7 +7207,7 @@
         <v>131</v>
       </c>
       <c r="E137" s="21" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F137" s="22" t="str">
         <f>IF(OR(E137="",E137="!!!"),"",IF(NOT(ISNA(VLOOKUP(E137,E$1:E136,1,FALSE()))),"OLD",IF(AND(E137&lt;&gt;"",E137&lt;&gt;"!!!"),"NEW","")))</f>
@@ -7587,13 +7642,9 @@
       <c r="D149" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E149" s="21" t="str">
-        <f t="shared" si="16"/>
-        <v>!!!</v>
-      </c>
-      <c r="F149" s="22" t="str">
-        <f>IF(OR(E149="",E149="!!!"),"",IF(NOT(ISNA(VLOOKUP(E149,E$1:E148,1,FALSE()))),"OLD",IF(AND(E149&lt;&gt;"",E149&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
+      <c r="E149" s="21"/>
+      <c r="F149" s="22" t="s">
+        <v>426</v>
       </c>
       <c r="G149" s="23" t="str">
         <f>IF(OR(E149="",E149="!!!"),"",IF(OR(J149=0,AND(J149=1,K149=1),AND(J149=1,I149="SBJ"),AND(J149=1,I149=0)),"?IN_FOCUS",IF(J149&lt;=2,"?ACTIVATED",IF(J149&lt;&gt;"","?FAMILIAR",IF(F149="NEW",IF(ISNA(VLOOKUP(E149,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
@@ -7662,7 +7713,7 @@
         <v>207</v>
       </c>
       <c r="E151" s="21" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F151" s="22" t="str">
         <f>IF(OR(E151="",E151="!!!"),"",IF(NOT(ISNA(VLOOKUP(E151,E$1:E150,1,FALSE()))),"OLD",IF(AND(E151&lt;&gt;"",E151&lt;&gt;"!!!"),"NEW","")))</f>
@@ -7689,7 +7740,7 @@
         <v>0</v>
       </c>
       <c r="L151" s="26" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
@@ -7778,7 +7829,7 @@
         <v>254</v>
       </c>
       <c r="E156" s="21" t="str">
-        <f t="shared" ref="E155:E178" si="19">IF(D156="?OLD","!!!","")</f>
+        <f t="shared" ref="E156:E178" si="19">IF(D156="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F156" s="22" t="str">
@@ -7924,7 +7975,7 @@
         <v>141</v>
       </c>
       <c r="E160" s="21" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F160" s="22" t="str">
         <f>IF(OR(E160="",E160="!!!"),"",IF(NOT(ISNA(VLOOKUP(E160,E$1:E159,1,FALSE()))),"OLD",IF(AND(E160&lt;&gt;"",E160&lt;&gt;"!!!"),"NEW","")))</f>
@@ -8033,17 +8084,16 @@
       <c r="D163" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E163" s="21" t="str">
-        <f t="shared" si="19"/>
-        <v>!!!</v>
+      <c r="E163" s="21" t="s">
+        <v>487</v>
       </c>
       <c r="F163" s="22" t="str">
         <f>IF(OR(E163="",E163="!!!"),"",IF(NOT(ISNA(VLOOKUP(E163,E$1:E162,1,FALSE()))),"OLD",IF(AND(E163&lt;&gt;"",E163&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
+        <v>NEW</v>
       </c>
       <c r="G163" s="23" t="str">
-        <f>IF(OR(E163="",E163="!!!"),"",IF(OR(J163=0,AND(J163=1,K163=1),AND(J163=1,I163="SBJ"),AND(J163=1,I163=0)),"?IN_FOCUS",IF(J163&lt;=2,"?ACTIVATED",IF(J163&lt;&gt;"","?FAMILIAR",IF(F163="NEW",IF(ISNA(VLOOKUP(E163,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v/>
+        <f ca="1">IF(OR(E163="",E163="!!!"),"",IF(OR(J163=0,AND(J163=1,K163=1),AND(J163=1,I163="SBJ"),AND(J163=1,I163=0)),"?IN_FOCUS",IF(J163&lt;=2,"?ACTIVATED",IF(J163&lt;&gt;"","?FAMILIAR",IF(F163="NEW",IF(ISNA(VLOOKUP(E163,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v>?REFERENTIAL</v>
       </c>
       <c r="H163" s="24" t="str">
         <f t="shared" ca="1" si="18"/>
@@ -8110,17 +8160,16 @@
       <c r="D165" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E165" s="21" t="str">
-        <f t="shared" si="19"/>
-        <v>!!!</v>
+      <c r="E165" s="21" t="s">
+        <v>488</v>
       </c>
       <c r="F165" s="22" t="str">
         <f>IF(OR(E165="",E165="!!!"),"",IF(NOT(ISNA(VLOOKUP(E165,E$1:E164,1,FALSE()))),"OLD",IF(AND(E165&lt;&gt;"",E165&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
+        <v>NEW</v>
       </c>
       <c r="G165" s="23" t="str">
-        <f>IF(OR(E165="",E165="!!!"),"",IF(OR(J165=0,AND(J165=1,K165=1),AND(J165=1,I165="SBJ"),AND(J165=1,I165=0)),"?IN_FOCUS",IF(J165&lt;=2,"?ACTIVATED",IF(J165&lt;&gt;"","?FAMILIAR",IF(F165="NEW",IF(ISNA(VLOOKUP(E165,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v/>
+        <f ca="1">IF(OR(E165="",E165="!!!"),"",IF(OR(J165=0,AND(J165=1,K165=1),AND(J165=1,I165="SBJ"),AND(J165=1,I165=0)),"?IN_FOCUS",IF(J165&lt;=2,"?ACTIVATED",IF(J165&lt;&gt;"","?FAMILIAR",IF(F165="NEW",IF(ISNA(VLOOKUP(E165,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v>?REFERENTIAL</v>
       </c>
       <c r="H165" s="24" t="str">
         <f t="shared" ca="1" si="18"/>
@@ -8286,17 +8335,16 @@
       <c r="C170" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="E170" s="21" t="str">
-        <f t="shared" si="19"/>
-        <v/>
+      <c r="E170" s="21" t="s">
+        <v>457</v>
       </c>
       <c r="F170" s="22" t="str">
         <f>IF(OR(E170="",E170="!!!"),"",IF(NOT(ISNA(VLOOKUP(E170,E$1:E169,1,FALSE()))),"OLD",IF(AND(E170&lt;&gt;"",E170&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
+        <v>OLD</v>
       </c>
       <c r="G170" s="23" t="str">
-        <f>IF(OR(E170="",E170="!!!"),"",IF(OR(J170=0,AND(J170=1,K170=1),AND(J170=1,I170="SBJ"),AND(J170=1,I170=0)),"?IN_FOCUS",IF(J170&lt;=2,"?ACTIVATED",IF(J170&lt;&gt;"","?FAMILIAR",IF(F170="NEW",IF(ISNA(VLOOKUP(E170,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v/>
+        <f ca="1">IF(OR(E170="",E170="!!!"),"",IF(OR(J170=0,AND(J170=1,K170=1),AND(J170=1,I170="SBJ"),AND(J170=1,I170=0)),"?IN_FOCUS",IF(J170&lt;=2,"?ACTIVATED",IF(J170&lt;&gt;"","?FAMILIAR",IF(F170="NEW",IF(ISNA(VLOOKUP(E170,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v>?IN_FOCUS</v>
       </c>
       <c r="H170" s="24" t="str">
         <f t="shared" ca="1" si="18"/>
@@ -8304,15 +8352,15 @@
       </c>
       <c r="I170" s="25" t="str">
         <f>IF(OR(E170="",E170="!!!",F170="NEW"),"",INDEX(B$2:B169,-1+SUMPRODUCT(MAX(ROW(E$2:E169)*(E170=E$2:E169)))))</f>
-        <v/>
-      </c>
-      <c r="J170" s="25" t="str">
+        <v>other_2</v>
+      </c>
+      <c r="J170" s="25">
         <f ca="1">IF(OR(E170="",E170="!!!",F170="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E170)*(E170=E$2:E170)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E169)*(E2=E$1:E169))))))</f>
-        <v/>
-      </c>
-      <c r="K170" s="25" t="str">
-        <f>IF(OR(E170="",E170="!!!",F170="NEW"),"",INDEX(J$1:J169,SUMPRODUCT(MAX(ROW(E$1:E169)*(E170=E$1:E169)))))</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="K170" s="25">
+        <f ca="1">IF(OR(E170="",E170="!!!",F170="NEW"),"",INDEX(J$1:J169,SUMPRODUCT(MAX(ROW(E$1:E169)*(E170=E$1:E169)))))</f>
+        <v>0</v>
       </c>
       <c r="L170" s="26"/>
     </row>
@@ -8656,7 +8704,7 @@
         <v>179</v>
       </c>
       <c r="E182" s="21" t="str">
-        <f t="shared" ref="E181:E194" si="21">IF(D182="?OLD","!!!","")</f>
+        <f t="shared" ref="E182:E194" si="21">IF(D182="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F182" s="22" t="str">
@@ -8794,7 +8842,9 @@
         <f>IF(OR(E185="",E185="!!!",F185="NEW"),"",INDEX(J$1:J184,SUMPRODUCT(MAX(ROW(E$1:E184)*(E185=E$1:E184)))))</f>
         <v/>
       </c>
-      <c r="L185" s="26"/>
+      <c r="L185" s="26" t="s">
+        <v>489</v>
+      </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
@@ -8844,7 +8894,7 @@
         <v>131</v>
       </c>
       <c r="E187" s="21" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F187" s="22" t="str">
         <f>IF(OR(E187="",E187="!!!"),"",IF(NOT(ISNA(VLOOKUP(E187,E$1:E186,1,FALSE()))),"OLD",IF(AND(E187&lt;&gt;"",E187&lt;&gt;"!!!"),"NEW","")))</f>
@@ -9056,7 +9106,7 @@
         <v>131</v>
       </c>
       <c r="E193" s="21" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F193" s="22" t="str">
         <f>IF(OR(E193="",E193="!!!"),"",IF(NOT(ISNA(VLOOKUP(E193,E$1:E192,1,FALSE()))),"OLD",IF(AND(E193&lt;&gt;"",E193&lt;&gt;"!!!"),"NEW","")))</f>
@@ -9171,7 +9221,7 @@
         <v>131</v>
       </c>
       <c r="E198" s="21" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F198" s="22" t="str">
         <f>IF(OR(E198="",E198="!!!"),"",IF(NOT(ISNA(VLOOKUP(E198,E$1:E197,1,FALSE()))),"OLD",IF(AND(E198&lt;&gt;"",E198&lt;&gt;"!!!"),"NEW","")))</f>
@@ -9422,7 +9472,7 @@
         <v>131</v>
       </c>
       <c r="E207" s="21" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F207" s="22" t="str">
         <f>IF(OR(E207="",E207="!!!"),"",IF(NOT(ISNA(VLOOKUP(E207,E$1:E206,1,FALSE()))),"OLD",IF(AND(E207&lt;&gt;"",E207&lt;&gt;"!!!"),"NEW","")))</f>
@@ -9608,7 +9658,7 @@
         <v>131</v>
       </c>
       <c r="E212" s="21" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F212" s="22" t="str">
         <f>IF(OR(E212="",E212="!!!"),"",IF(NOT(ISNA(VLOOKUP(E212,E$1:E211,1,FALSE()))),"OLD",IF(AND(E212&lt;&gt;"",E212&lt;&gt;"!!!"),"NEW","")))</f>
@@ -9717,13 +9767,9 @@
       <c r="D215" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E215" s="21" t="str">
-        <f t="shared" si="24"/>
-        <v>!!!</v>
-      </c>
-      <c r="F215" s="22" t="str">
-        <f>IF(OR(E215="",E215="!!!"),"",IF(NOT(ISNA(VLOOKUP(E215,E$1:E214,1,FALSE()))),"OLD",IF(AND(E215&lt;&gt;"",E215&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
+      <c r="E215" s="21"/>
+      <c r="F215" s="22" t="s">
+        <v>490</v>
       </c>
       <c r="G215" s="23" t="str">
         <f>IF(OR(E215="",E215="!!!"),"",IF(OR(J215=0,AND(J215=1,K215=1),AND(J215=1,I215="SBJ"),AND(J215=1,I215=0)),"?IN_FOCUS",IF(J215&lt;=2,"?ACTIVATED",IF(J215&lt;&gt;"","?FAMILIAR",IF(F215="NEW",IF(ISNA(VLOOKUP(E215,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
@@ -9937,7 +9983,7 @@
         <v>131</v>
       </c>
       <c r="E221" s="21" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F221" s="22" t="str">
         <f>IF(OR(E221="",E221="!!!"),"",IF(NOT(ISNA(VLOOKUP(E221,E$1:E220,1,FALSE()))),"OLD",IF(AND(E221&lt;&gt;"",E221&lt;&gt;"!!!"),"NEW","")))</f>
@@ -10049,10 +10095,10 @@
         <v>207</v>
       </c>
       <c r="E226" s="21" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F226" s="22" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G226" s="23" t="e">
         <f ca="1">IF(OR(E226="",E226="!!!"),"",IF(OR(J226=0,AND(J226=1,K226=1),AND(J226=1,I226="SBJ"),AND(J226=1,I226=0)),"?IN_FOCUS",IF(J226&lt;=2,"?ACTIVATED",IF(J226&lt;&gt;"","?FAMILIAR",IF(F226="NEW",IF(ISNA(VLOOKUP(E226,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
@@ -10075,7 +10121,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="L226" s="26" t="s">
-        <v>470</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.3">
@@ -10127,7 +10173,7 @@
       </c>
       <c r="E228" s="21"/>
       <c r="F228" s="22" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G228" s="23" t="str">
         <f>IF(OR(E228="",E228="!!!"),"",IF(OR(J228=0,AND(J228=1,K228=1),AND(J228=1,I228="SBJ"),AND(J228=1,I228=0)),"?IN_FOCUS",IF(J228&lt;=2,"?ACTIVATED",IF(J228&lt;&gt;"","?FAMILIAR",IF(F228="NEW",IF(ISNA(VLOOKUP(E228,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
@@ -10348,7 +10394,7 @@
         <v>131</v>
       </c>
       <c r="E236" s="21" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F236" s="22" t="str">
         <f>IF(OR(E236="",E236="!!!"),"",IF(NOT(ISNA(VLOOKUP(E236,E$1:E235,1,FALSE()))),"OLD",IF(AND(E236&lt;&gt;"",E236&lt;&gt;"!!!"),"NEW","")))</f>
@@ -10381,7 +10427,7 @@
         <v>198</v>
       </c>
       <c r="E237" s="21" t="str">
-        <f t="shared" ref="E236:E249" si="29">IF(D237="?OLD","!!!","")</f>
+        <f t="shared" ref="E237:E249" si="29">IF(D237="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F237" s="22" t="str">
@@ -10424,7 +10470,7 @@
         <v>131</v>
       </c>
       <c r="E238" s="21" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F238" s="22" t="str">
         <f>IF(OR(E238="",E238="!!!"),"",IF(NOT(ISNA(VLOOKUP(E238,E$1:E237,1,FALSE()))),"OLD",IF(AND(E238&lt;&gt;"",E238&lt;&gt;"!!!"),"NEW","")))</f>
@@ -10534,7 +10580,7 @@
         <v>131</v>
       </c>
       <c r="E241" s="21" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F241" s="22" t="str">
         <f>IF(OR(E241="",E241="!!!"),"",IF(NOT(ISNA(VLOOKUP(E241,E$1:E240,1,FALSE()))),"OLD",IF(AND(E241&lt;&gt;"",E241&lt;&gt;"!!!"),"NEW","")))</f>
@@ -10955,7 +11001,7 @@
         <v>131</v>
       </c>
       <c r="E255" s="21" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F255" s="22" t="str">
         <f>IF(OR(E255="",E255="!!!"),"",IF(NOT(ISNA(VLOOKUP(E255,E$1:E254,1,FALSE()))),"OLD",IF(AND(E255&lt;&gt;"",E255&lt;&gt;"!!!"),"NEW","")))</f>
@@ -11339,7 +11385,9 @@
         <f>IF(OR(E267="",E267="!!!",F267="NEW"),"",INDEX(J$1:J266,SUMPRODUCT(MAX(ROW(E$1:E266)*(E267=E$1:E266)))))</f>
         <v/>
       </c>
-      <c r="L267" s="26"/>
+      <c r="L267" s="26" t="s">
+        <v>492</v>
+      </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
@@ -11434,7 +11482,7 @@
         <v>131</v>
       </c>
       <c r="E272" s="21" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F272" s="22" t="str">
         <f>IF(OR(E272="",E272="!!!"),"",IF(NOT(ISNA(VLOOKUP(E272,E$1:E271,1,FALSE()))),"OLD",IF(AND(E272&lt;&gt;"",E272&lt;&gt;"!!!"),"NEW","")))</f>
@@ -11549,7 +11597,7 @@
         <v>131</v>
       </c>
       <c r="E277" s="21" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F277" s="22" t="str">
         <f>IF(OR(E277="",E277="!!!"),"",IF(NOT(ISNA(VLOOKUP(E277,E$1:E276,1,FALSE()))),"OLD",IF(AND(E277&lt;&gt;"",E277&lt;&gt;"!!!"),"NEW","")))</f>
@@ -11735,10 +11783,10 @@
         <v>131</v>
       </c>
       <c r="E282" s="21" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F282" s="22" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="G282" s="23" t="str">
         <f ca="1">IF(OR(E282="",E282="!!!"),"",IF(OR(J282=0,AND(J282=1,K282=1),AND(J282=1,I282="SBJ"),AND(J282=1,I282=0)),"?IN_FOCUS",IF(J282&lt;=2,"?ACTIVATED",IF(J282&lt;&gt;"","?FAMILIAR",IF(F282="NEW",IF(ISNA(VLOOKUP(E282,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
@@ -11844,7 +11892,7 @@
         <v>131</v>
       </c>
       <c r="E285" s="21" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F285" s="22" t="str">
         <f>IF(OR(E285="",E285="!!!"),"",IF(NOT(ISNA(VLOOKUP(E285,E$1:E284,1,FALSE()))),"OLD",IF(AND(E285&lt;&gt;"",E285&lt;&gt;"!!!"),"NEW","")))</f>
@@ -11871,7 +11919,7 @@
         <v/>
       </c>
       <c r="L285" s="26" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.3">
@@ -11889,7 +11937,7 @@
       </c>
       <c r="E286" s="21"/>
       <c r="F286" s="22" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G286" s="23" t="str">
         <f>IF(OR(E286="",E286="!!!"),"",IF(OR(J286=0,AND(J286=1,K286=1),AND(J286=1,I286="SBJ"),AND(J286=1,I286=0)),"?IN_FOCUS",IF(J286&lt;=2,"?ACTIVATED",IF(J286&lt;&gt;"","?FAMILIAR",IF(F286="NEW",IF(ISNA(VLOOKUP(E286,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
@@ -11912,7 +11960,7 @@
         <v/>
       </c>
       <c r="L286" s="26" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.3">
@@ -12129,7 +12177,7 @@
         <v/>
       </c>
       <c r="L294" s="26" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.3">
@@ -12146,7 +12194,7 @@
         <v>131</v>
       </c>
       <c r="E295" s="21" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F295" s="22" t="str">
         <f>IF(OR(E295="",E295="!!!"),"",IF(NOT(ISNA(VLOOKUP(E295,E$1:E294,1,FALSE()))),"OLD",IF(AND(E295&lt;&gt;"",E295&lt;&gt;"!!!"),"NEW","")))</f>
@@ -12583,7 +12631,7 @@
         <v>131</v>
       </c>
       <c r="E307" s="21" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F307" s="22" t="str">
         <f>IF(OR(E307="",E307="!!!"),"",IF(NOT(ISNA(VLOOKUP(E307,E$1:E306,1,FALSE()))),"OLD",IF(AND(E307&lt;&gt;"",E307&lt;&gt;"!!!"),"NEW","")))</f>
@@ -13626,7 +13674,7 @@
         <v>131</v>
       </c>
       <c r="E340" s="21" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="F340" s="22" t="str">
         <f>IF(OR(E340="",E340="!!!"),"",IF(NOT(ISNA(VLOOKUP(E340,E$1:E339,1,FALSE()))),"OLD",IF(AND(E340&lt;&gt;"",E340&lt;&gt;"!!!"),"NEW","")))</f>
@@ -13763,7 +13811,9 @@
         <f>IF(OR(E343="",E343="!!!",F343="NEW"),"",INDEX(J$1:J342,SUMPRODUCT(MAX(ROW(E$1:E342)*(E343=E$1:E342)))))</f>
         <v/>
       </c>
-      <c r="L343" s="26"/>
+      <c r="L343" s="26" t="s">
+        <v>489</v>
+      </c>
     </row>
     <row r="344" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
@@ -14053,15 +14103,15 @@
         <v>165</v>
       </c>
       <c r="E354" s="21" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="F354" s="22" t="str">
         <f>IF(OR(E354="",E354="!!!"),"",IF(NOT(ISNA(VLOOKUP(E354,E$1:E353,1,FALSE()))),"OLD",IF(AND(E354&lt;&gt;"",E354&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
+        <v>NEW</v>
       </c>
       <c r="G354" s="23" t="str">
-        <f>IF(OR(E354="",E354="!!!"),"",IF(OR(J354=0,AND(J354=1,K354=1),AND(J354=1,I354="SBJ"),AND(J354=1,I354=0)),"?IN_FOCUS",IF(J354&lt;=2,"?ACTIVATED",IF(J354&lt;&gt;"","?FAMILIAR",IF(F354="NEW",IF(ISNA(VLOOKUP(E354,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v/>
+        <f ca="1">IF(OR(E354="",E354="!!!"),"",IF(OR(J354=0,AND(J354=1,K354=1),AND(J354=1,I354="SBJ"),AND(J354=1,I354=0)),"?IN_FOCUS",IF(J354&lt;=2,"?ACTIVATED",IF(J354&lt;&gt;"","?FAMILIAR",IF(F354="NEW",IF(ISNA(VLOOKUP(E354,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v>?REFERENTIAL</v>
       </c>
       <c r="H354" s="24" t="str">
         <f t="shared" ca="1" si="41"/>
@@ -14080,7 +14130,7 @@
         <v/>
       </c>
       <c r="L354" s="26" t="s">
-        <v>425</v>
+        <v>493</v>
       </c>
     </row>
     <row r="355" spans="1:12" x14ac:dyDescent="0.3">
@@ -14122,7 +14172,7 @@
         <v/>
       </c>
       <c r="L355" s="26" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="356" spans="1:12" x14ac:dyDescent="0.3">
@@ -14207,7 +14257,7 @@
         <v>131</v>
       </c>
       <c r="E358" s="21" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F358" s="22" t="str">
         <f>IF(OR(E358="",E358="!!!"),"",IF(NOT(ISNA(VLOOKUP(E358,E$1:E357,1,FALSE()))),"OLD",IF(AND(E358&lt;&gt;"",E358&lt;&gt;"!!!"),"NEW","")))</f>
@@ -14234,7 +14284,7 @@
         <v/>
       </c>
       <c r="L358" s="26" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="359" spans="1:12" x14ac:dyDescent="0.3">
@@ -14303,7 +14353,7 @@
         <v>0</v>
       </c>
       <c r="L360" s="26" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="361" spans="1:12" x14ac:dyDescent="0.3">
@@ -14388,10 +14438,10 @@
         <v>131</v>
       </c>
       <c r="E363" s="21" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F363" s="22" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="G363" s="23" t="str">
         <f ca="1">IF(OR(E363="",E363="!!!"),"",IF(OR(J363=0,AND(J363=1,K363=1),AND(J363=1,I363="SBJ"),AND(J363=1,I363=0)),"?IN_FOCUS",IF(J363&lt;=2,"?ACTIVATED",IF(J363&lt;&gt;"","?FAMILIAR",IF(F363="NEW",IF(ISNA(VLOOKUP(E363,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
@@ -14531,7 +14581,7 @@
         <v>131</v>
       </c>
       <c r="E367" s="21" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F367" s="22" t="str">
         <f>IF(OR(E367="",E367="!!!"),"",IF(NOT(ISNA(VLOOKUP(E367,E$1:E366,1,FALSE()))),"OLD",IF(AND(E367&lt;&gt;"",E367&lt;&gt;"!!!"),"NEW","")))</f>
@@ -14923,16 +14973,15 @@
       <c r="D380" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E380" s="21" t="str">
-        <f t="shared" si="42"/>
-        <v>!!!</v>
+      <c r="E380" s="21" t="s">
+        <v>494</v>
       </c>
       <c r="F380" s="22" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="G380" s="23" t="str">
-        <f>IF(OR(E380="",E380="!!!"),"",IF(OR(J380=0,AND(J380=1,K380=1),AND(J380=1,I380="SBJ"),AND(J380=1,I380=0)),"?IN_FOCUS",IF(J380&lt;=2,"?ACTIVATED",IF(J380&lt;&gt;"","?FAMILIAR",IF(F380="NEW",IF(ISNA(VLOOKUP(E380,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v/>
+        <f ca="1">IF(OR(E380="",E380="!!!"),"",IF(OR(J380=0,AND(J380=1,K380=1),AND(J380=1,I380="SBJ"),AND(J380=1,I380=0)),"?IN_FOCUS",IF(J380&lt;=2,"?ACTIVATED",IF(J380&lt;&gt;"","?FAMILIAR",IF(F380="NEW",IF(ISNA(VLOOKUP(E380,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v>?IN_FOCUS</v>
       </c>
       <c r="H380" s="24" t="str">
         <f t="shared" ca="1" si="43"/>
@@ -14940,14 +14989,14 @@
       </c>
       <c r="I380" s="25" t="str">
         <f>IF(OR(E380="",E380="!!!",F380="NEW"),"",INDEX(B$2:B379,-1+SUMPRODUCT(MAX(ROW(E$2:E379)*(E380=E$2:E379)))))</f>
-        <v/>
-      </c>
-      <c r="J380" s="25" t="str">
+        <v>other</v>
+      </c>
+      <c r="J380" s="25">
         <f ca="1">IF(OR(E380="",E380="!!!",F380="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E380)*(E380=E$2:E380)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E379)*(E2=E$1:E379))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K380" s="25" t="str">
-        <f>IF(OR(E380="",E380="!!!",F380="NEW"),"",INDEX(J$1:J379,SUMPRODUCT(MAX(ROW(E$1:E379)*(E380=E$1:E379)))))</f>
+        <f ca="1">IF(OR(E380="",E380="!!!",F380="NEW"),"",INDEX(J$1:J379,SUMPRODUCT(MAX(ROW(E$1:E379)*(E380=E$1:E379)))))</f>
         <v/>
       </c>
       <c r="L380" s="26"/>
@@ -15062,7 +15111,7 @@
         <v/>
       </c>
       <c r="L383" s="26" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="384" spans="1:12" x14ac:dyDescent="0.3">
@@ -15079,7 +15128,7 @@
         <v>131</v>
       </c>
       <c r="E384" s="21" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F384" s="22" t="str">
         <f>IF(OR(E384="",E384="!!!"),"",IF(NOT(ISNA(VLOOKUP(E384,E$1:E383,1,FALSE()))),"OLD",IF(AND(E384&lt;&gt;"",E384&lt;&gt;"!!!"),"NEW","")))</f>
@@ -15189,7 +15238,7 @@
         <v>131</v>
       </c>
       <c r="E387" s="21" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F387" s="22" t="str">
         <f>IF(OR(E387="",E387="!!!"),"",IF(NOT(ISNA(VLOOKUP(E387,E$1:E386,1,FALSE()))),"OLD",IF(AND(E387&lt;&gt;"",E387&lt;&gt;"!!!"),"NEW","")))</f>
@@ -15361,7 +15410,7 @@
         <v/>
       </c>
       <c r="L391" s="26" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="392" spans="1:12" x14ac:dyDescent="0.3">
@@ -15378,7 +15427,7 @@
         <v>131</v>
       </c>
       <c r="E392" s="21" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F392" s="22" t="str">
         <f>IF(OR(E392="",E392="!!!"),"",IF(NOT(ISNA(VLOOKUP(E392,E$1:E391,1,FALSE()))),"OLD",IF(AND(E392&lt;&gt;"",E392&lt;&gt;"!!!"),"NEW","")))</f>
@@ -15550,7 +15599,7 @@
         <v/>
       </c>
       <c r="L396" s="26" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="397" spans="1:12" x14ac:dyDescent="0.3">
@@ -15567,7 +15616,7 @@
         <v>131</v>
       </c>
       <c r="E397" s="21" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F397" s="22" t="str">
         <f>IF(OR(E397="",E397="!!!"),"",IF(NOT(ISNA(VLOOKUP(E397,E$1:E396,1,FALSE()))),"OLD",IF(AND(E397&lt;&gt;"",E397&lt;&gt;"!!!"),"NEW","")))</f>
@@ -15677,7 +15726,7 @@
         <v>131</v>
       </c>
       <c r="E400" s="21" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F400" s="22" t="str">
         <f>IF(OR(E400="",E400="!!!"),"",IF(NOT(ISNA(VLOOKUP(E400,E$1:E399,1,FALSE()))),"OLD",IF(AND(E400&lt;&gt;"",E400&lt;&gt;"!!!"),"NEW","")))</f>
@@ -15787,7 +15836,7 @@
         <v>131</v>
       </c>
       <c r="E403" s="21" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F403" s="22" t="str">
         <f>IF(OR(E403="",E403="!!!"),"",IF(NOT(ISNA(VLOOKUP(E403,E$1:E402,1,FALSE()))),"OLD",IF(AND(E403&lt;&gt;"",E403&lt;&gt;"!!!"),"NEW","")))</f>
@@ -15959,7 +16008,7 @@
         <v/>
       </c>
       <c r="L407" s="26" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="408" spans="1:12" x14ac:dyDescent="0.3">
@@ -15976,7 +16025,7 @@
         <v>131</v>
       </c>
       <c r="E408" s="21" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F408" s="22" t="str">
         <f>IF(OR(E408="",E408="!!!"),"",IF(NOT(ISNA(VLOOKUP(E408,E$1:E407,1,FALSE()))),"OLD",IF(AND(E408&lt;&gt;"",E408&lt;&gt;"!!!"),"NEW","")))</f>
@@ -16043,7 +16092,7 @@
         <v>385</v>
       </c>
       <c r="E410" s="21" t="str">
-        <f t="shared" ref="E410:E441" si="44">IF(D410="?OLD","!!!","")</f>
+        <f t="shared" ref="E410:E434" si="44">IF(D410="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F410" s="22" t="str">
@@ -16055,7 +16104,7 @@
         <v/>
       </c>
       <c r="H410" s="24" t="str">
-        <f t="shared" ref="H410:H441" ca="1" si="45">IF(J410&lt;&gt;1,"",IF(I410="SBJ","CB","?"))</f>
+        <f t="shared" ref="H410:H434" ca="1" si="45">IF(J410&lt;&gt;1,"",IF(I410="SBJ","CB","?"))</f>
         <v/>
       </c>
       <c r="I410" s="25" t="str">
@@ -16182,7 +16231,7 @@
         <v/>
       </c>
       <c r="L413" s="26" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="414" spans="1:12" x14ac:dyDescent="0.3">
@@ -16267,7 +16316,7 @@
         <v>131</v>
       </c>
       <c r="E416" s="21" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F416" s="22" t="str">
         <f>IF(OR(E416="",E416="!!!"),"",IF(NOT(ISNA(VLOOKUP(E416,E$1:E415,1,FALSE()))),"OLD",IF(AND(E416&lt;&gt;"",E416&lt;&gt;"!!!"),"NEW","")))</f>
@@ -16439,7 +16488,7 @@
         <v/>
       </c>
       <c r="L420" s="26" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="421" spans="1:12" x14ac:dyDescent="0.3">
@@ -16447,7 +16496,7 @@
         <v>392</v>
       </c>
       <c r="E421" s="21" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F421" s="22" t="str">
         <f>IF(OR(E421="",E421="!!!"),"",IF(NOT(ISNA(VLOOKUP(E421,E$1:E420,1,FALSE()))),"OLD",IF(AND(E421&lt;&gt;"",E421&lt;&gt;"!!!"),"NEW","")))</f>
@@ -16621,7 +16670,7 @@
         <v/>
       </c>
       <c r="L425" s="26" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="426" spans="1:12" x14ac:dyDescent="0.3">
@@ -16638,7 +16687,7 @@
         <v>131</v>
       </c>
       <c r="E426" s="21" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F426" s="22" t="str">
         <f>IF(OR(E426="",E426="!!!"),"",IF(NOT(ISNA(VLOOKUP(E426,E$1:E425,1,FALSE()))),"OLD",IF(AND(E426&lt;&gt;"",E426&lt;&gt;"!!!"),"NEW","")))</f>
@@ -16773,7 +16822,7 @@
         <v/>
       </c>
       <c r="L429" s="26" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="430" spans="1:12" x14ac:dyDescent="0.3">
@@ -16852,7 +16901,7 @@
         <v/>
       </c>
       <c r="L431" s="26" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="432" spans="1:12" x14ac:dyDescent="0.3">
@@ -16869,7 +16918,7 @@
         <v>131</v>
       </c>
       <c r="E432" s="21" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F432" s="22" t="str">
         <f>IF(OR(E432="",E432="!!!"),"",IF(NOT(ISNA(VLOOKUP(E432,E$1:E431,1,FALSE()))),"OLD",IF(AND(E432&lt;&gt;"",E432&lt;&gt;"!!!"),"NEW","")))</f>
@@ -16983,20 +17032,19 @@
       <c r="D437" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E437" s="21" t="str">
-        <f t="shared" ref="E437:E447" si="46">IF(D437="?OLD","!!!","")</f>
-        <v>!!!</v>
+      <c r="E437" s="21" t="s">
+        <v>496</v>
       </c>
       <c r="F437" s="22" t="str">
         <f>IF(OR(E437="",E437="!!!"),"",IF(NOT(ISNA(VLOOKUP(E437,E$1:E436,1,FALSE()))),"OLD",IF(AND(E437&lt;&gt;"",E437&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
+        <v>NEW</v>
       </c>
       <c r="G437" s="23" t="str">
-        <f>IF(OR(E437="",E437="!!!"),"",IF(OR(J437=0,AND(J437=1,K437=1),AND(J437=1,I437="SBJ"),AND(J437=1,I437=0)),"?IN_FOCUS",IF(J437&lt;=2,"?ACTIVATED",IF(J437&lt;&gt;"","?FAMILIAR",IF(F437="NEW",IF(ISNA(VLOOKUP(E437,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v/>
+        <f ca="1">IF(OR(E437="",E437="!!!"),"",IF(OR(J437=0,AND(J437=1,K437=1),AND(J437=1,I437="SBJ"),AND(J437=1,I437=0)),"?IN_FOCUS",IF(J437&lt;=2,"?ACTIVATED",IF(J437&lt;&gt;"","?FAMILIAR",IF(F437="NEW",IF(ISNA(VLOOKUP(E437,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v>?REFERENTIAL</v>
       </c>
       <c r="H437" s="24" t="str">
-        <f t="shared" ref="H437:H447" ca="1" si="47">IF(J437&lt;&gt;1,"",IF(I437="SBJ","CB","?"))</f>
+        <f t="shared" ref="H437:H447" ca="1" si="46">IF(J437&lt;&gt;1,"",IF(I437="SBJ","CB","?"))</f>
         <v/>
       </c>
       <c r="I437" s="25" t="str">
@@ -17011,7 +17059,9 @@
         <f>IF(OR(E437="",E437="!!!",F437="NEW"),"",INDEX(J$1:J436,SUMPRODUCT(MAX(ROW(E$1:E436)*(E437=E$1:E436)))))</f>
         <v/>
       </c>
-      <c r="L437" s="26"/>
+      <c r="L437" s="26" t="s">
+        <v>495</v>
+      </c>
     </row>
     <row r="438" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
@@ -17036,7 +17086,7 @@
         <v/>
       </c>
       <c r="H438" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="I438" s="25" t="str">
@@ -17052,7 +17102,7 @@
         <v/>
       </c>
       <c r="L438" s="26" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="439" spans="1:12" x14ac:dyDescent="0.3">
@@ -17068,33 +17118,32 @@
       <c r="D439" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E439" s="21" t="str">
-        <f t="shared" si="46"/>
-        <v>!!!</v>
+      <c r="E439" s="21" t="s">
+        <v>494</v>
       </c>
       <c r="F439" s="22" t="str">
         <f>IF(OR(E439="",E439="!!!"),"",IF(NOT(ISNA(VLOOKUP(E439,E$1:E438,1,FALSE()))),"OLD",IF(AND(E439&lt;&gt;"",E439&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
+        <v>OLD</v>
       </c>
       <c r="G439" s="23" t="str">
-        <f>IF(OR(E439="",E439="!!!"),"",IF(OR(J439=0,AND(J439=1,K439=1),AND(J439=1,I439="SBJ"),AND(J439=1,I439=0)),"?IN_FOCUS",IF(J439&lt;=2,"?ACTIVATED",IF(J439&lt;&gt;"","?FAMILIAR",IF(F439="NEW",IF(ISNA(VLOOKUP(E439,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v/>
+        <f ca="1">IF(OR(E439="",E439="!!!"),"",IF(OR(J439=0,AND(J439=1,K439=1),AND(J439=1,I439="SBJ"),AND(J439=1,I439=0)),"?IN_FOCUS",IF(J439&lt;=2,"?ACTIVATED",IF(J439&lt;&gt;"","?FAMILIAR",IF(F439="NEW",IF(ISNA(VLOOKUP(E439,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v>?IN_FOCUS</v>
       </c>
       <c r="H439" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="I439" s="25" t="str">
         <f>IF(OR(E439="",E439="!!!",F439="NEW"),"",INDEX(B$2:B438,-1+SUMPRODUCT(MAX(ROW(E$2:E438)*(E439=E$2:E438)))))</f>
-        <v/>
-      </c>
-      <c r="J439" s="25" t="str">
+        <v>other</v>
+      </c>
+      <c r="J439" s="25">
         <f ca="1">IF(OR(E439="",E439="!!!",F439="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E439)*(E439=E$2:E439)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E438)*(E2=E$1:E438))))))</f>
-        <v/>
-      </c>
-      <c r="K439" s="25" t="str">
-        <f>IF(OR(E439="",E439="!!!",F439="NEW"),"",INDEX(J$1:J438,SUMPRODUCT(MAX(ROW(E$1:E438)*(E439=E$1:E438)))))</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="K439" s="25">
+        <f ca="1">IF(OR(E439="",E439="!!!",F439="NEW"),"",INDEX(J$1:J438,SUMPRODUCT(MAX(ROW(E$1:E438)*(E439=E$1:E438)))))</f>
+        <v>0</v>
       </c>
       <c r="L439" s="26"/>
     </row>
@@ -17103,7 +17152,7 @@
         <v>405</v>
       </c>
       <c r="E440" s="21" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" ref="E437:E447" si="47">IF(D440="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F440" s="22" t="str">
@@ -17115,7 +17164,7 @@
         <v/>
       </c>
       <c r="H440" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="I440" s="25" t="str">
@@ -17137,7 +17186,7 @@
         <v>171</v>
       </c>
       <c r="E441" s="21" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="F441" s="22" t="str">
@@ -17149,7 +17198,7 @@
         <v/>
       </c>
       <c r="H441" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="I441" s="25" t="str">
@@ -17171,7 +17220,7 @@
         <v>143</v>
       </c>
       <c r="E442" s="21" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="F442" s="22" t="str">
@@ -17183,7 +17232,7 @@
         <v/>
       </c>
       <c r="H442" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="I442" s="25" t="str">
@@ -17214,17 +17263,17 @@
         <v>131</v>
       </c>
       <c r="E443" s="21" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F443" s="22" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="G443" s="23" t="str">
         <f ca="1">IF(OR(E443="",E443="!!!"),"",IF(OR(J443=0,AND(J443=1,K443=1),AND(J443=1,I443="SBJ"),AND(J443=1,I443=0)),"?IN_FOCUS",IF(J443&lt;=2,"?ACTIVATED",IF(J443&lt;&gt;"","?FAMILIAR",IF(F443="NEW",IF(ISNA(VLOOKUP(E443,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
         <v>?IN_FOCUS</v>
       </c>
       <c r="H443" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="I443" s="25" t="str">
@@ -17246,7 +17295,7 @@
         <v>205</v>
       </c>
       <c r="E444" s="21" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="F444" s="22" t="str">
@@ -17258,7 +17307,7 @@
         <v/>
       </c>
       <c r="H444" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="I444" s="25" t="str">
@@ -17289,7 +17338,7 @@
         <v>131</v>
       </c>
       <c r="E445" s="21" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F445" s="22" t="str">
         <f>IF(OR(E445="",E445="!!!"),"",IF(NOT(ISNA(VLOOKUP(E445,E$1:E444,1,FALSE()))),"OLD",IF(AND(E445&lt;&gt;"",E445&lt;&gt;"!!!"),"NEW","")))</f>
@@ -17300,7 +17349,7 @@
         <v>?IN_FOCUS</v>
       </c>
       <c r="H445" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="I445" s="25" t="str">
@@ -17322,7 +17371,7 @@
         <v>406</v>
       </c>
       <c r="E446" s="21" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="F446" s="22" t="str">
@@ -17334,7 +17383,7 @@
         <v/>
       </c>
       <c r="H446" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="I446" s="25" t="str">
@@ -17356,7 +17405,7 @@
         <v>148</v>
       </c>
       <c r="E447" s="21" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="F447" s="22" t="str">
@@ -17368,7 +17417,7 @@
         <v/>
       </c>
       <c r="H447" s="24" t="str">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="46"/>
         <v/>
       </c>
       <c r="I447" s="25" t="str">
@@ -17505,17 +17554,16 @@
       <c r="D453" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E453" s="21" t="str">
-        <f t="shared" si="48"/>
-        <v>!!!</v>
+      <c r="E453" s="21" t="s">
+        <v>497</v>
       </c>
       <c r="F453" s="22" t="str">
         <f>IF(OR(E453="",E453="!!!"),"",IF(NOT(ISNA(VLOOKUP(E453,E$1:E452,1,FALSE()))),"OLD",IF(AND(E453&lt;&gt;"",E453&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
+        <v>NEW</v>
       </c>
       <c r="G453" s="23" t="str">
-        <f>IF(OR(E453="",E453="!!!"),"",IF(OR(J453=0,AND(J453=1,K453=1),AND(J453=1,I453="SBJ"),AND(J453=1,I453=0)),"?IN_FOCUS",IF(J453&lt;=2,"?ACTIVATED",IF(J453&lt;&gt;"","?FAMILIAR",IF(F453="NEW",IF(ISNA(VLOOKUP(E453,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v/>
+        <f ca="1">IF(OR(E453="",E453="!!!"),"",IF(OR(J453=0,AND(J453=1,K453=1),AND(J453=1,I453="SBJ"),AND(J453=1,I453=0)),"?IN_FOCUS",IF(J453&lt;=2,"?ACTIVATED",IF(J453&lt;&gt;"","?FAMILIAR",IF(F453="NEW",IF(ISNA(VLOOKUP(E453,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v>?REFERENTIAL</v>
       </c>
       <c r="H453" s="24" t="str">
         <f t="shared" ca="1" si="49"/>
@@ -17650,17 +17698,16 @@
       <c r="D457" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E457" s="21" t="str">
-        <f t="shared" si="48"/>
-        <v>!!!</v>
+      <c r="E457" s="21" t="s">
+        <v>496</v>
       </c>
       <c r="F457" s="22" t="str">
         <f>IF(OR(E457="",E457="!!!"),"",IF(NOT(ISNA(VLOOKUP(E457,E$1:E456,1,FALSE()))),"OLD",IF(AND(E457&lt;&gt;"",E457&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
+        <v>OLD</v>
       </c>
       <c r="G457" s="23" t="str">
-        <f>IF(OR(E457="",E457="!!!"),"",IF(OR(J457=0,AND(J457=1,K457=1),AND(J457=1,I457="SBJ"),AND(J457=1,I457=0)),"?IN_FOCUS",IF(J457&lt;=2,"?ACTIVATED",IF(J457&lt;&gt;"","?FAMILIAR",IF(F457="NEW",IF(ISNA(VLOOKUP(E457,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v/>
+        <f ca="1">IF(OR(E457="",E457="!!!"),"",IF(OR(J457=0,AND(J457=1,K457=1),AND(J457=1,I457="SBJ"),AND(J457=1,I457=0)),"?IN_FOCUS",IF(J457&lt;=2,"?ACTIVATED",IF(J457&lt;&gt;"","?FAMILIAR",IF(F457="NEW",IF(ISNA(VLOOKUP(E457,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v>?IN_FOCUS</v>
       </c>
       <c r="H457" s="24" t="str">
         <f t="shared" ca="1" si="49"/>
@@ -17668,14 +17715,14 @@
       </c>
       <c r="I457" s="25" t="str">
         <f>IF(OR(E457="",E457="!!!",F457="NEW"),"",INDEX(B$2:B456,-1+SUMPRODUCT(MAX(ROW(E$2:E456)*(E457=E$2:E456)))))</f>
-        <v/>
-      </c>
-      <c r="J457" s="25" t="str">
+        <v>SBJ</v>
+      </c>
+      <c r="J457" s="25">
         <f ca="1">IF(OR(E457="",E457="!!!",F457="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E457)*(E457=E$2:E457)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E456)*(E2=E$1:E456))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K457" s="25" t="str">
-        <f>IF(OR(E457="",E457="!!!",F457="NEW"),"",INDEX(J$1:J456,SUMPRODUCT(MAX(ROW(E$1:E456)*(E457=E$1:E456)))))</f>
+        <f ca="1">IF(OR(E457="",E457="!!!",F457="NEW"),"",INDEX(J$1:J456,SUMPRODUCT(MAX(ROW(E$1:E456)*(E457=E$1:E456)))))</f>
         <v/>
       </c>
       <c r="L457" s="26"/>
@@ -17762,7 +17809,7 @@
         <v>131</v>
       </c>
       <c r="E460" s="21" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F460" s="22" t="str">
         <f>IF(OR(E460="",E460="!!!"),"",IF(NOT(ISNA(VLOOKUP(E460,E$1:E459,1,FALSE()))),"OLD",IF(AND(E460&lt;&gt;"",E460&lt;&gt;"!!!"),"NEW","")))</f>
@@ -17931,7 +17978,7 @@
         <v/>
       </c>
       <c r="L464" s="26" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="465" spans="1:12" x14ac:dyDescent="0.3">
@@ -17973,7 +18020,7 @@
         <v>417</v>
       </c>
       <c r="E466" s="21" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F466" s="22" t="str">
         <f>IF(OR(E466="",E466="!!!"),"",IF(NOT(ISNA(VLOOKUP(E466,E$1:E465,1,FALSE()))),"OLD",IF(AND(E466&lt;&gt;"",E466&lt;&gt;"!!!"),"NEW","")))</f>
@@ -18121,7 +18168,7 @@
         <v>132</v>
       </c>
       <c r="E472" s="21" t="str">
-        <f t="shared" ref="E471:E479" si="51">IF(D472="?OLD","!!!","")</f>
+        <f t="shared" ref="E472:E479" si="51">IF(D472="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F472" s="22" t="str">
@@ -18346,7 +18393,7 @@
         <v>131</v>
       </c>
       <c r="E478" s="21" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F478" s="22" t="str">
         <f>IF(OR(E478="",E478="!!!"),"",IF(NOT(ISNA(VLOOKUP(E478,E$1:E477,1,FALSE()))),"OLD",IF(AND(E478&lt;&gt;"",E478&lt;&gt;"!!!"),"NEW","")))</f>
